--- a/sheets/국악이꽃피는나무/검수/조각배.xlsx
+++ b/sheets/국악이꽃피는나무/검수/조각배.xlsx
@@ -2800,28 +2800,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -3142,7 +3142,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -3165,7 +3165,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3344,7 +3344,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3423,7 +3423,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3445,7 +3445,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60.61" customHeight="true">
+    <row r="16" ht="64.52" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="90.2" customHeight="true">
+    <row r="17" ht="96.05" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="90.2" customHeight="true">
+    <row r="18" ht="96.05" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="90.2" customHeight="true">
+    <row r="19" ht="96.05" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -3560,7 +3560,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="90.2" customHeight="true">
+    <row r="20" ht="96.05" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -3579,7 +3579,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="90.2" customHeight="true">
+    <row r="21" ht="96.05" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -3598,7 +3598,7 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="90.2" customHeight="true">
+    <row r="22" ht="96.05" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -3617,7 +3617,7 @@
       <c r="P22" s="21"/>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="90.2" customHeight="true">
+    <row r="23" ht="96.05" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="90.2" customHeight="true">
+    <row r="24" ht="96.05" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="90.2" customHeight="true">
+    <row r="25" ht="96.05" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -3709,7 +3709,7 @@
       <c r="P25" s="21"/>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="90.2" customHeight="true">
+    <row r="26" ht="96.05" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -3728,7 +3728,7 @@
       <c r="P26" s="21"/>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="90.2" customHeight="true">
+    <row r="27" ht="96.05" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -3747,7 +3747,7 @@
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="90.2" customHeight="true">
+    <row r="28" ht="96.05" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -3777,7 +3777,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
